--- a/backend/data/feedback.xlsx
+++ b/backend/data/feedback.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="27">
   <si>
     <t>Timestamp</t>
   </si>
@@ -52,6 +52,9 @@
     <t>2026-02-13 19:16:41</t>
   </si>
   <si>
+    <t>2026-02-16 11:12:56</t>
+  </si>
+  <si>
     <t>Akash</t>
   </si>
   <si>
@@ -89,6 +92,9 @@
   </si>
   <si>
     <t>ghjghgjhg</t>
+  </si>
+  <si>
+    <t>Persistant metrics card popups. Information popups and all other modals are persistent across tabs.</t>
   </si>
 </sst>
 </file>
@@ -446,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -474,19 +480,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -494,19 +500,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -514,19 +520,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -534,16 +540,16 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -551,16 +557,16 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -568,19 +574,39 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7">
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
